--- a/Monthly loan.xlsx
+++ b/Monthly loan.xlsx
@@ -7,16 +7,25 @@
     <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760"/>
   </bookViews>
   <sheets>
-    <sheet name="Ramabhati" sheetId="16" r:id="rId1"/>
-    <sheet name="Nanao" sheetId="17" r:id="rId2"/>
-    <sheet name="Sunanda" sheetId="18" r:id="rId3"/>
+    <sheet name="CompleteList" sheetId="21" r:id="rId1"/>
+    <sheet name="Ramabhati" sheetId="16" r:id="rId2"/>
+    <sheet name="Nanao" sheetId="17" r:id="rId3"/>
+    <sheet name="priyadarsini" sheetId="18" r:id="rId4"/>
+    <sheet name="anand" sheetId="23" r:id="rId5"/>
+    <sheet name="naoton" sheetId="22" r:id="rId6"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CompleteList!$C$1:$D$2</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="18">
   <si>
     <t>Date</t>
   </si>
@@ -25,6 +34,51 @@
   </si>
   <si>
     <t>Details</t>
+  </si>
+  <si>
+    <t>TrendAnalysis Cash Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest for Rs 300000/ </t>
+  </si>
+  <si>
+    <t>Outstanding Interest</t>
+  </si>
+  <si>
+    <t>Total Interest Collected</t>
+  </si>
+  <si>
+    <t>Total Outstanding Interest</t>
+  </si>
+  <si>
+    <t>Benao</t>
+  </si>
+  <si>
+    <t>Tungfam</t>
+  </si>
+  <si>
+    <t>Rambhabati</t>
+  </si>
+  <si>
+    <t>Nanao</t>
+  </si>
+  <si>
+    <t>Priyadarshini</t>
+  </si>
+  <si>
+    <t>Naoton</t>
+  </si>
+  <si>
+    <t>Anand</t>
+  </si>
+  <si>
+    <t>Loanee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest Collected </t>
+  </si>
+  <si>
+    <t>Outstg Interest</t>
   </si>
 </sst>
 </file>
@@ -35,7 +89,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="[$₹-4009]#,##0.00;[Red]\-[$₹-4009]#,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -44,6 +98,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Segoe UI"/>
@@ -70,7 +131,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -93,11 +154,95 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="4" tint="0.39994506668294322"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thick">
+        <color theme="4" tint="0.39994506668294322"/>
+      </top>
+      <bottom style="thick">
+        <color theme="4" tint="0.39994506668294322"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thick">
+        <color theme="4" tint="0.39994506668294322"/>
+      </top>
+      <bottom style="thick">
+        <color theme="4" tint="0.39994506668294322"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thick">
+        <color theme="4" tint="0.39994506668294322"/>
+      </right>
+      <top style="thick">
+        <color theme="4" tint="0.39994506668294322"/>
+      </top>
+      <bottom style="thick">
+        <color theme="4" tint="0.39994506668294322"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -107,6 +252,30 @@
     </xf>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -132,6 +301,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="2023TrendAnalysis"/>
+      <sheetName val="2025TrendAnalysis"/>
+      <sheetName val="2026TrendAnalysis"/>
+      <sheetName val="trackingonline transaction"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="67">
+          <cell r="G67">
+            <v>17700</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -397,7 +591,414 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D27"/>
+  <dimension ref="B1:E17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="4"/>
+    <col min="2" max="2" width="12.7109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="41.42578125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="22" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3">
+        <f>'[1]2026TrendAnalysis'!$G$67</f>
+        <v>17700</v>
+      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="1"/>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3">
+        <f>SUM(D7:D17)</f>
+        <v>49250</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="1"/>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3">
+        <f>SUM(E7:E17)</f>
+        <v>-31050</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="1"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="2:5" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="6"/>
+      <c r="C6" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="14">
+        <v>1</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="10">
+        <f>Ramabhati!D2</f>
+        <v>37450</v>
+      </c>
+      <c r="E7" s="10">
+        <f>Ramabhati!D3</f>
+        <v>-30050</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="14">
+        <v>2</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3">
+        <f>Nanao!D2</f>
+        <v>800</v>
+      </c>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="14">
+        <v>3</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="3">
+        <f>priyadarsini!D2</f>
+        <v>8000</v>
+      </c>
+      <c r="E9" s="3">
+        <f>priyadarsini!F7</f>
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="14">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="3">
+        <f>naoton!D2</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <f>naoton!D3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="14">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="3">
+        <f>anand!D2</f>
+        <v>3000</v>
+      </c>
+      <c r="E11" s="3">
+        <f>anand!D3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="1"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="1"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="1"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="1"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="1"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:D22"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="4"/>
+    <col min="2" max="2" width="12.7109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="41.42578125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" style="4" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5">
+        <f>SUM(C5:C22)</f>
+        <v>37450</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="5">
+        <f>SUM(D5:D13)</f>
+        <v>-30050</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>45915</v>
+      </c>
+      <c r="C5" s="10">
+        <v>7500</v>
+      </c>
+      <c r="D5" s="3">
+        <f>C5-7500</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C6" s="10">
+        <v>7500</v>
+      </c>
+      <c r="D6" s="3">
+        <f t="shared" ref="D6:D13" si="0">C6-7500</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>45976</v>
+      </c>
+      <c r="C7" s="10">
+        <v>7500</v>
+      </c>
+      <c r="D7" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>46006</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <f t="shared" si="0"/>
+        <v>-7500</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>46037</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <f t="shared" si="0"/>
+        <v>-7500</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>46068</v>
+      </c>
+      <c r="C10" s="10">
+        <v>7500</v>
+      </c>
+      <c r="D10" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
+        <v>46096</v>
+      </c>
+      <c r="C11" s="10">
+        <v>3550</v>
+      </c>
+      <c r="D11" s="3">
+        <f t="shared" si="0"/>
+        <v>-3950</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <v>46127</v>
+      </c>
+      <c r="C12" s="10">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <f t="shared" si="0"/>
+        <v>-7500</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
+        <v>46157</v>
+      </c>
+      <c r="C13" s="10">
+        <v>3900</v>
+      </c>
+      <c r="D13" s="3">
+        <f t="shared" si="0"/>
+        <v>-3600</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="1">
+        <v>46188</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="1">
+        <v>46249</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="1">
+        <v>46280</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="1">
+        <v>46310</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="1">
+        <v>46341</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="1">
+        <v>46371</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="1">
+        <v>46402</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22" s="1">
+        <v>46433</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:D28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
@@ -407,30 +1008,42 @@
     <col min="5" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
+    <row r="2" spans="2:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5">
+        <f>SUM(C4:C21)</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="13" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
-      <c r="C4" s="2"/>
+    <row r="4" spans="2:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>46127</v>
+      </c>
+      <c r="C4" s="10">
+        <v>400</v>
+      </c>
       <c r="D4" s="3"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B5" s="1"/>
-      <c r="C5" s="2"/>
+      <c r="B5" s="1">
+        <v>46157</v>
+      </c>
+      <c r="C5" s="10">
+        <v>400</v>
+      </c>
       <c r="D5" s="3"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.3">
@@ -542,6 +1155,11 @@
       <c r="B27" s="1"/>
       <c r="C27" s="2"/>
       <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B28" s="1"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -549,153 +1167,155 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D27"/>
+  <dimension ref="B2:F13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
     <col min="2" max="2" width="12.7109375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" style="4" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="4"/>
+    <col min="3" max="3" width="19.85546875" style="4" customWidth="1"/>
+    <col min="4" max="5" width="16.5703125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5">
+        <f>SUM(E5:E13)</f>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="5">
+        <f>SUM(F5:F13)</f>
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="23.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B5" s="1"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="1"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="1"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="1"/>
+      <c r="D4" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>46096</v>
+      </c>
+      <c r="C5" s="10">
+        <v>6000</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F5" s="3">
+        <f>C5-6000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>46127</v>
+      </c>
+      <c r="C6" s="10">
+        <v>6000</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F6" s="3">
+        <f t="shared" ref="F6:F7" si="0">C6-6000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>46157</v>
+      </c>
+      <c r="C7" s="10">
+        <v>5000</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" si="0"/>
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>46188</v>
+      </c>
       <c r="C8" s="2"/>
       <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="1"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>46218</v>
+      </c>
       <c r="C9" s="2"/>
       <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="1"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>46249</v>
+      </c>
       <c r="C10" s="2"/>
       <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="1"/>
       <c r="C11" s="2"/>
       <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="1"/>
       <c r="C12" s="2"/>
       <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
       <c r="C13" s="2"/>
       <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B14" s="1"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B15" s="1"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B16" s="1"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B17" s="1"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" s="1"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="1"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B20" s="1"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B21" s="1"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B22" s="1"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B23" s="1"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B24" s="1"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B25" s="1"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B26" s="1"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="3"/>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B27" s="1"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -703,51 +1323,324 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D27"/>
+  <dimension ref="B2:F29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
     <col min="2" max="2" width="12.7109375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" style="4" customWidth="1"/>
+    <col min="4" max="5" width="16.5703125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5">
+        <f>SUM(E5:E29)</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="5">
+        <f>SUM(F5:F29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>46096</v>
+      </c>
+      <c r="C5" s="3">
+        <v>7000</v>
+      </c>
+      <c r="D5" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>46127</v>
+      </c>
+      <c r="C6" s="3">
+        <v>7000</v>
+      </c>
+      <c r="D6" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>46157</v>
+      </c>
+      <c r="C7" s="3">
+        <v>7000</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>46188</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>46249</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="1"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="1"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="1"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="1"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="1"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="1"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="1"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="1"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="1"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="1"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="1"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="1"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="1"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="1"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="1"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="1"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="1"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="1"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="1"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:D20"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="4"/>
+    <col min="2" max="2" width="12.7109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" style="4" customWidth="1"/>
     <col min="5" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5">
+        <f>SUM(C5:C20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="5">
+        <f>SUM(D5:D20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B5" s="1"/>
+      <c r="D4" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>46188</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="3"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="1"/>
+      <c r="B6" s="1">
+        <v>46218</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="1"/>
+      <c r="B7" s="1">
+        <v>46249</v>
+      </c>
       <c r="C7" s="2"/>
       <c r="D7" s="3"/>
     </row>
@@ -815,41 +1708,6 @@
       <c r="B20" s="1"/>
       <c r="C20" s="2"/>
       <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B21" s="1"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B22" s="1"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B23" s="1"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B24" s="1"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B25" s="1"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B26" s="1"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="3"/>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B27" s="1"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Monthly loan.xlsx
+++ b/Monthly loan.xlsx
@@ -4,19 +4,17 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="CompleteList" sheetId="21" r:id="rId1"/>
     <sheet name="Ramabhati" sheetId="16" r:id="rId2"/>
-    <sheet name="Nanao" sheetId="17" r:id="rId3"/>
-    <sheet name="priyadarsini" sheetId="18" r:id="rId4"/>
-    <sheet name="anand" sheetId="23" r:id="rId5"/>
-    <sheet name="naoton" sheetId="22" r:id="rId6"/>
+    <sheet name="Sunanda" sheetId="24" r:id="rId3"/>
+    <sheet name="Nanao" sheetId="17" r:id="rId4"/>
+    <sheet name="priyadarsini" sheetId="18" r:id="rId5"/>
+    <sheet name="anand" sheetId="23" r:id="rId6"/>
+    <sheet name="naoton" sheetId="22" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CompleteList!$C$1:$D$2</definedName>
   </definedNames>
@@ -25,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="19">
   <si>
     <t>Date</t>
   </si>
@@ -34,12 +32,6 @@
   </si>
   <si>
     <t>Details</t>
-  </si>
-  <si>
-    <t>TrendAnalysis Cash Balance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interest for Rs 300000/ </t>
   </si>
   <si>
     <t>Outstanding Interest</t>
@@ -79,6 +71,15 @@
   </si>
   <si>
     <t>Outstg Interest</t>
+  </si>
+  <si>
+    <t>Sunanda</t>
+  </si>
+  <si>
+    <t>2.5% Interest for Rs 120000 = 3000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5% Interest for Rs 300000 = 7500 </t>
   </si>
 </sst>
 </file>
@@ -242,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -276,6 +277,8 @@
     <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -301,31 +304,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="2023TrendAnalysis"/>
-      <sheetName val="2025TrendAnalysis"/>
-      <sheetName val="2026TrendAnalysis"/>
-      <sheetName val="trackingonline transaction"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="67">
-          <cell r="G67">
-            <v>17700</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -591,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:E17"/>
+  <dimension ref="B1:E18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
@@ -610,34 +588,29 @@
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="3">
-        <f>'[1]2026TrendAnalysis'!$G$67</f>
-        <v>17700</v>
-      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3">
-        <f>SUM(D7:D17)</f>
-        <v>49250</v>
+        <f>SUM(D7:D18)</f>
+        <v>59750</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="1"/>
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3">
-        <f>SUM(E7:E17)</f>
-        <v>-31050</v>
+        <f>SUM(E7:E18)</f>
+        <v>-51550</v>
       </c>
       <c r="E4" s="3"/>
     </row>
@@ -650,13 +623,13 @@
     <row r="6" spans="2:5" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="6"/>
       <c r="C6" s="11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
@@ -664,7 +637,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" s="10">
         <f>Ramabhati!D2</f>
@@ -679,45 +652,45 @@
       <c r="B8" s="14">
         <v>2</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="3">
-        <f>Nanao!D2</f>
-        <v>800</v>
-      </c>
-      <c r="E8" s="3"/>
+      <c r="C8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="10">
+        <f>Sunanda!D2</f>
+        <v>9500</v>
+      </c>
+      <c r="E8" s="10">
+        <f>Sunanda!D3</f>
+        <v>-20500</v>
+      </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="14">
         <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D9" s="3">
-        <f>priyadarsini!D2</f>
-        <v>8000</v>
-      </c>
-      <c r="E9" s="3">
-        <f>priyadarsini!F7</f>
-        <v>-1000</v>
-      </c>
+        <f>Nanao!D2</f>
+        <v>800</v>
+      </c>
+      <c r="E9" s="3"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="14">
         <v>4</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D10" s="3">
-        <f>naoton!D2</f>
-        <v>0</v>
+        <f>priyadarsini!D2</f>
+        <v>8000</v>
       </c>
       <c r="E10" s="3">
-        <f>naoton!D3</f>
-        <v>0</v>
+        <f>priyadarsini!F7</f>
+        <v>-1000</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
@@ -725,22 +698,30 @@
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D11" s="3">
-        <f>anand!D2</f>
-        <v>3000</v>
+        <f>naoton!D2</f>
+        <v>0</v>
       </c>
       <c r="E11" s="3">
-        <f>anand!D3</f>
+        <f>naoton!D3</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="1"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="C12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="3">
+        <f>anand!D2</f>
+        <v>4000</v>
+      </c>
+      <c r="E12" s="3">
+        <f>anand!D3</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
@@ -771,6 +752,11 @@
       <c r="C17" s="2"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C18" s="2"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -780,7 +766,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D22"/>
+  <dimension ref="B2:G22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
@@ -790,36 +776,36 @@
     <col min="5" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C2" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" s="5">
         <f>SUM(C5:C22)</f>
         <v>37450</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3" s="5">
         <f>SUM(D5:D13)</f>
         <v>-30050</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:7" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>45915</v>
       </c>
@@ -831,7 +817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>45945</v>
       </c>
@@ -843,7 +829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>45976</v>
       </c>
@@ -854,8 +840,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="G7" s="16"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>46006</v>
       </c>
@@ -867,7 +854,7 @@
         <v>-7500</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>46037</v>
       </c>
@@ -879,7 +866,7 @@
         <v>-7500</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>46068</v>
       </c>
@@ -891,7 +878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>46096</v>
       </c>
@@ -903,7 +890,7 @@
         <v>-3950</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>46127</v>
       </c>
@@ -915,7 +902,7 @@
         <v>-7500</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>46157</v>
       </c>
@@ -927,21 +914,21 @@
         <v>-3600</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <v>46188</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="1">
         <v>46218</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="3"/>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>46249</v>
       </c>
@@ -997,6 +984,234 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:H22"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="4"/>
+    <col min="2" max="2" width="12.7109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="41.42578125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" style="4" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="5">
+        <f>SUM(C5:C22)</f>
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5">
+        <f>SUM(D5:D24)</f>
+        <v>-20500</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>45915</v>
+      </c>
+      <c r="C5" s="10">
+        <f>500*2</f>
+        <v>1000</v>
+      </c>
+      <c r="D5" s="3">
+        <f>C5-3000</f>
+        <v>-2000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C6" s="10">
+        <f>500*9</f>
+        <v>4500</v>
+      </c>
+      <c r="D6" s="3">
+        <f t="shared" ref="D6:D14" si="0">C6-3000</f>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>45976</v>
+      </c>
+      <c r="C7" s="10">
+        <f>500*3</f>
+        <v>1500</v>
+      </c>
+      <c r="D7" s="3">
+        <f t="shared" si="0"/>
+        <v>-1500</v>
+      </c>
+      <c r="H7" s="15"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>46006</v>
+      </c>
+      <c r="C8" s="10">
+        <f>500*2</f>
+        <v>1000</v>
+      </c>
+      <c r="D8" s="3">
+        <f t="shared" si="0"/>
+        <v>-2000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>46037</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <f t="shared" si="0"/>
+        <v>-3000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>46068</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <f t="shared" si="0"/>
+        <v>-3000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
+        <v>46096</v>
+      </c>
+      <c r="C11" s="10">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <f t="shared" si="0"/>
+        <v>-3000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <v>46127</v>
+      </c>
+      <c r="C12" s="10">
+        <v>500</v>
+      </c>
+      <c r="D12" s="3">
+        <f t="shared" si="0"/>
+        <v>-2500</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
+        <v>46157</v>
+      </c>
+      <c r="C13" s="10">
+        <v>500</v>
+      </c>
+      <c r="D13" s="3">
+        <f t="shared" si="0"/>
+        <v>-2500</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="1">
+        <v>46188</v>
+      </c>
+      <c r="C14" s="10">
+        <v>500</v>
+      </c>
+      <c r="D14" s="3">
+        <f t="shared" si="0"/>
+        <v>-2500</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="1">
+        <v>46249</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="1">
+        <v>46280</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="1">
+        <v>46310</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="1">
+        <v>46341</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="1">
+        <v>46371</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="1">
+        <v>46402</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22" s="1">
+        <v>46433</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1010,7 +1225,7 @@
   <sheetData>
     <row r="2" spans="2:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C2" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" s="5">
         <f>SUM(C4:C21)</f>
@@ -1167,7 +1382,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1182,7 +1397,7 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C2" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" s="5">
         <f>SUM(E5:E13)</f>
@@ -1191,7 +1406,7 @@
     </row>
     <row r="3" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3" s="5">
         <f>SUM(F5:F13)</f>
@@ -1206,13 +1421,13 @@
         <v>1</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
@@ -1323,7 +1538,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1338,16 +1553,16 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C2" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" s="5">
         <f>SUM(E5:E29)</f>
-        <v>3000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3" s="5">
         <f>SUM(F5:F29)</f>
@@ -1362,13 +1577,13 @@
         <v>1</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
@@ -1418,11 +1633,17 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
-        <v>46188</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+        <v>46191</v>
+      </c>
+      <c r="C8" s="3">
+        <v>7000</v>
+      </c>
+      <c r="D8" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1000</v>
+      </c>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
@@ -1582,7 +1803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1596,7 +1817,7 @@
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C2" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" s="5">
         <f>SUM(C5:C20)</f>
@@ -1605,7 +1826,7 @@
     </row>
     <row r="3" spans="2:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3" s="5">
         <f>SUM(D5:D20)</f>
@@ -1620,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">

--- a/Monthly loan.xlsx
+++ b/Monthly loan.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="4800" windowWidth="20640" windowHeight="11760" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="CompleteList" sheetId="21" r:id="rId1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" s="3">
         <f>SUM(E7:E18)</f>
-        <v>-51550</v>
+        <v>-54550</v>
       </c>
       <c r="E4" s="3"/>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="E8" s="10">
         <f>Sunanda!D3</f>
-        <v>-20500</v>
+        <v>-23500</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D3" s="5">
         <f>SUM(D5:D24)</f>
-        <v>-20500</v>
+        <v>-23500</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1046,7 +1046,7 @@
         <v>4500</v>
       </c>
       <c r="D6" s="3">
-        <f t="shared" ref="D6:D14" si="0">C6-3000</f>
+        <f t="shared" ref="D6:D15" si="0">C6-3000</f>
         <v>1500</v>
       </c>
     </row>
@@ -1153,8 +1153,13 @@
       <c r="B15" s="1">
         <v>46218</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="3"/>
+      <c r="C15" s="10">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <f t="shared" si="0"/>
+        <v>-3000</v>
+      </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
